--- a/docs/html/fase2/muestra_datos_m05.xlsx
+++ b/docs/html/fase2/muestra_datos_m05.xlsx
@@ -10214,11 +10214,11 @@
         <v>74765</v>
       </c>
       <c r="B159" t="n">
-        <v>1334708</v>
+        <v>1069732</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Rumania</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Castelló de la Plana</t>
+          <t>Vila-real</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10252,17 +10252,17 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="L159" t="n">
-        <v>8.468</v>
+        <v>8.748000000000001</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11018,7 +11018,7 @@
         <v>46290</v>
       </c>
       <c r="B172" t="n">
-        <v>1000488</v>
+        <v>1067522</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -11059,10 +11059,10 @@
         <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="L172" t="n">
-        <v>7.382000000000001</v>
+        <v>6.297000000000001</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -23020,11 +23020,11 @@
         <v>24954</v>
       </c>
       <c r="B366" t="n">
-        <v>805088</v>
+        <v>592302</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -23034,17 +23034,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Castelló</t>
+          <t>València</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Castelló de la Plana</t>
+          <t>València</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23058,17 +23058,17 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K366" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="L366" t="n">
-        <v>7.5</v>
+        <v>5.79</v>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
